--- a/docs/Mapping_casi_uso/cittadinanza/Citt_044.xlsx
+++ b/docs/Mapping_casi_uso/cittadinanza/Citt_044.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="129">
   <si>
     <t>Sezione</t>
   </si>
@@ -137,7 +137,16 @@
     <t>estremiDecretoConferimento</t>
   </si>
   <si>
-    <t>Sindaco</t>
+    <t xml:space="preserve">Officiante </t>
+  </si>
+  <si>
+    <t>Ufficiale di stato civile delegato al giuramento di cittadinanza</t>
+  </si>
+  <si>
+    <t>officiante</t>
+  </si>
+  <si>
+    <t>opzionale</t>
   </si>
   <si>
     <t>Cognome</t>
@@ -147,9 +156,6 @@
   </si>
   <si>
     <t>cognome</t>
-  </si>
-  <si>
-    <t>opzionale</t>
   </si>
   <si>
     <t>Nome</t>
@@ -451,11 +457,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H124"/>
+  <dimension ref="A1:H125"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="16.125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="49.37109375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="55.49609375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.5625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="37.0390625" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="27.421875" customWidth="true" bestFit="true"/>
@@ -865,16 +871,16 @@
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="19">
@@ -882,13 +888,13 @@
         <v>41</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>47</v>
@@ -897,7 +903,7 @@
         <v>10</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20">
@@ -908,10 +914,10 @@
         <v>48</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>49</v>
@@ -920,7 +926,7 @@
         <v>10</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
@@ -934,7 +940,7 @@
         <v>35</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>51</v>
@@ -943,7 +949,7 @@
         <v>10</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22">
@@ -957,7 +963,7 @@
         <v>35</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>53</v>
@@ -966,7 +972,7 @@
         <v>10</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23">
@@ -980,7 +986,7 @@
         <v>35</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>55</v>
@@ -989,7 +995,7 @@
         <v>10</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24">
@@ -1003,7 +1009,7 @@
         <v>35</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>57</v>
@@ -1012,7 +1018,7 @@
         <v>10</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25">
@@ -1026,7 +1032,7 @@
         <v>35</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>59</v>
@@ -1035,7 +1041,7 @@
         <v>10</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26">
@@ -1049,7 +1055,7 @@
         <v>35</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>61</v>
@@ -1058,7 +1064,7 @@
         <v>10</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27">
@@ -1072,7 +1078,7 @@
         <v>35</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>63</v>
@@ -1081,7 +1087,7 @@
         <v>10</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28">
@@ -1095,7 +1101,7 @@
         <v>35</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>65</v>
@@ -1104,7 +1110,7 @@
         <v>10</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29">
@@ -1118,7 +1124,7 @@
         <v>35</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>67</v>
@@ -1127,7 +1133,7 @@
         <v>10</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30">
@@ -1141,7 +1147,7 @@
         <v>35</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>69</v>
@@ -1150,7 +1156,7 @@
         <v>10</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31">
@@ -1164,7 +1170,7 @@
         <v>35</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>71</v>
@@ -1173,7 +1179,7 @@
         <v>10</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32">
@@ -1187,7 +1193,7 @@
         <v>35</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>73</v>
@@ -1196,7 +1202,7 @@
         <v>10</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33">
@@ -1210,7 +1216,7 @@
         <v>35</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>75</v>
@@ -1219,7 +1225,7 @@
         <v>10</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34">
@@ -1233,7 +1239,7 @@
         <v>35</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>77</v>
@@ -1242,7 +1248,7 @@
         <v>10</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35">
@@ -1256,7 +1262,7 @@
         <v>35</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>79</v>
@@ -1265,7 +1271,7 @@
         <v>10</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36">
@@ -1279,7 +1285,7 @@
         <v>35</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>81</v>
@@ -1288,7 +1294,7 @@
         <v>10</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37">
@@ -1302,7 +1308,7 @@
         <v>35</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>83</v>
@@ -1311,7 +1317,7 @@
         <v>10</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38">
@@ -1325,7 +1331,7 @@
         <v>35</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>85</v>
@@ -1334,7 +1340,7 @@
         <v>10</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39">
@@ -1348,7 +1354,7 @@
         <v>35</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>87</v>
@@ -1357,7 +1363,7 @@
         <v>10</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40">
@@ -1368,10 +1374,10 @@
         <v>88</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>89</v>
@@ -1380,7 +1386,7 @@
         <v>10</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41">
@@ -1394,7 +1400,7 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>91</v>
@@ -1403,7 +1409,7 @@
         <v>10</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42">
@@ -1414,10 +1420,10 @@
         <v>92</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>93</v>
@@ -1426,50 +1432,50 @@
         <v>10</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="C43" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="F43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>47</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>23</v>
@@ -1477,22 +1483,22 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>23</v>
@@ -1500,22 +1506,22 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>23</v>
@@ -1523,16 +1529,16 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>51</v>
@@ -1546,7 +1552,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>52</v>
@@ -1555,7 +1561,7 @@
         <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>53</v>
@@ -1569,16 +1575,16 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>55</v>
@@ -1592,16 +1598,16 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>57</v>
@@ -1615,16 +1621,16 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>59</v>
@@ -1638,22 +1644,22 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>61</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>23</v>
@@ -1661,22 +1667,22 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>63</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>23</v>
@@ -1684,22 +1690,22 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>65</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>23</v>
@@ -1707,16 +1713,16 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>67</v>
@@ -1730,22 +1736,22 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>23</v>
@@ -1753,16 +1759,16 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>71</v>
@@ -1776,22 +1782,22 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>73</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>23</v>
@@ -1799,22 +1805,22 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>23</v>
@@ -1822,22 +1828,22 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>77</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>23</v>
@@ -1845,22 +1851,22 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>79</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>23</v>
@@ -1868,22 +1874,22 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>81</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>23</v>
@@ -1891,22 +1897,22 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>83</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>23</v>
@@ -1914,22 +1920,22 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>85</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>23</v>
@@ -1937,16 +1943,16 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>87</v>
@@ -1960,22 +1966,22 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>23</v>
@@ -1983,7 +1989,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>114</v>
@@ -1992,13 +1998,13 @@
         <v>35</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>115</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>23</v>
@@ -2006,7 +2012,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>116</v>
@@ -2015,13 +2021,13 @@
         <v>35</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>117</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>23</v>
@@ -2029,7 +2035,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>118</v>
@@ -2038,13 +2044,13 @@
         <v>35</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>119</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>23</v>
@@ -2052,22 +2058,22 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>23</v>
@@ -2075,7 +2081,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>90</v>
@@ -2084,7 +2090,7 @@
         <v>9</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>91</v>
@@ -2098,16 +2104,16 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>93</v>
@@ -2121,22 +2127,22 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>23</v>
@@ -2144,22 +2150,22 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>47</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>23</v>
@@ -2167,16 +2173,16 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>49</v>
@@ -2190,16 +2196,16 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>51</v>
@@ -2213,7 +2219,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>52</v>
@@ -2222,7 +2228,7 @@
         <v>9</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>53</v>
@@ -2236,7 +2242,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>54</v>
@@ -2245,7 +2251,7 @@
         <v>9</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>55</v>
@@ -2259,7 +2265,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>56</v>
@@ -2268,7 +2274,7 @@
         <v>9</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>57</v>
@@ -2282,16 +2288,16 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>59</v>
@@ -2305,7 +2311,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>60</v>
@@ -2314,13 +2320,13 @@
         <v>35</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>61</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>23</v>
@@ -2328,7 +2334,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>62</v>
@@ -2337,13 +2343,13 @@
         <v>35</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>63</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>23</v>
@@ -2351,7 +2357,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>64</v>
@@ -2360,13 +2366,13 @@
         <v>35</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>65</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>23</v>
@@ -2374,7 +2380,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>66</v>
@@ -2383,7 +2389,7 @@
         <v>35</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>67</v>
@@ -2397,22 +2403,22 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>69</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>23</v>
@@ -2420,7 +2426,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>70</v>
@@ -2429,7 +2435,7 @@
         <v>9</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>71</v>
@@ -2443,22 +2449,22 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>124</v>
+        <v>73</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>23</v>
@@ -2466,19 +2472,19 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>17</v>
@@ -2489,7 +2495,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>74</v>
@@ -2498,13 +2504,13 @@
         <v>35</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>75</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>23</v>
@@ -2512,7 +2518,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>76</v>
@@ -2521,13 +2527,13 @@
         <v>35</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>77</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>23</v>
@@ -2535,7 +2541,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>78</v>
@@ -2544,13 +2550,13 @@
         <v>35</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>79</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>23</v>
@@ -2558,7 +2564,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>80</v>
@@ -2567,13 +2573,13 @@
         <v>35</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>81</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>23</v>
@@ -2581,7 +2587,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>82</v>
@@ -2590,13 +2596,13 @@
         <v>35</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>83</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>23</v>
@@ -2604,7 +2610,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>84</v>
@@ -2613,13 +2619,13 @@
         <v>35</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>85</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>23</v>
@@ -2627,7 +2633,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>86</v>
@@ -2636,7 +2642,7 @@
         <v>35</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>87</v>
@@ -2650,22 +2656,22 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>89</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>23</v>
@@ -2673,7 +2679,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>90</v>
@@ -2682,7 +2688,7 @@
         <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>91</v>
@@ -2696,16 +2702,16 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>93</v>
@@ -2719,19 +2725,19 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>10</v>
@@ -2742,16 +2748,16 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>47</v>
@@ -2765,16 +2771,16 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>49</v>
@@ -2788,16 +2794,16 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>51</v>
@@ -2811,7 +2817,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>52</v>
@@ -2820,7 +2826,7 @@
         <v>9</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>53</v>
@@ -2834,7 +2840,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>54</v>
@@ -2843,7 +2849,7 @@
         <v>9</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>55</v>
@@ -2857,7 +2863,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>56</v>
@@ -2866,7 +2872,7 @@
         <v>9</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>57</v>
@@ -2880,16 +2886,16 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>59</v>
@@ -2903,7 +2909,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>60</v>
@@ -2912,7 +2918,7 @@
         <v>35</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>61</v>
@@ -2926,7 +2932,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>62</v>
@@ -2935,7 +2941,7 @@
         <v>35</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>63</v>
@@ -2949,7 +2955,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>64</v>
@@ -2958,7 +2964,7 @@
         <v>35</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>65</v>
@@ -2972,7 +2978,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>66</v>
@@ -2981,7 +2987,7 @@
         <v>35</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>67</v>
@@ -2995,16 +3001,16 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>69</v>
@@ -3018,7 +3024,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>70</v>
@@ -3027,7 +3033,7 @@
         <v>9</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>71</v>
@@ -3041,19 +3047,19 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>124</v>
+        <v>73</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>10</v>
@@ -3064,19 +3070,19 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B114" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B114" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="C114" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D114" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E114" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>10</v>
@@ -3087,7 +3093,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>74</v>
@@ -3096,7 +3102,7 @@
         <v>35</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>75</v>
@@ -3110,7 +3116,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>76</v>
@@ -3119,7 +3125,7 @@
         <v>35</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>77</v>
@@ -3133,7 +3139,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>78</v>
@@ -3142,7 +3148,7 @@
         <v>35</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>79</v>
@@ -3156,7 +3162,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>80</v>
@@ -3165,7 +3171,7 @@
         <v>35</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>81</v>
@@ -3179,7 +3185,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>82</v>
@@ -3188,7 +3194,7 @@
         <v>35</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>83</v>
@@ -3202,7 +3208,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>84</v>
@@ -3211,7 +3217,7 @@
         <v>35</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>85</v>
@@ -3225,7 +3231,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>86</v>
@@ -3234,7 +3240,7 @@
         <v>35</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>87</v>
@@ -3248,16 +3254,16 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>89</v>
@@ -3271,7 +3277,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>90</v>
@@ -3280,7 +3286,7 @@
         <v>9</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>91</v>
@@ -3294,7 +3300,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>92</v>
@@ -3303,7 +3309,7 @@
         <v>9</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>93</v>
@@ -3312,6 +3318,29 @@
         <v>10</v>
       </c>
       <c r="G124" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G125" s="2" t="s">
         <v>23</v>
       </c>
     </row>
